--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6451" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6451" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente un acteur PS. </t>
+    <t xml:space="preserve">
+Cet attribut représente un acteur PS.
+</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -360,7 +362,7 @@
 </t>
   </si>
   <si>
-    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, • U, pour les systèmes.</t>
+    <t>Type de nom : Valeur en fonction de l’auteur :  D, pour les personnes physiques, -U, pour les systèmes.</t>
   </si>
   <si>
     <t>D</t>
@@ -390,7 +392,7 @@
     <t>ActorPatient (LM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente l'acteur Patient. </t>
+    <t>Cet attribut représente l'acteur Patient.</t>
   </si>
   <si>
     <t>ActorPatient.XCN1</t>
@@ -451,7 +453,7 @@
     <t>ActorSNR (LM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente l'acteur SNR. </t>
+    <t>Cet attribut représente l'acteur SNR.</t>
   </si>
   <si>
     <t>ActorSNR.XCN1</t>
@@ -518,7 +520,7 @@
     <t>ActorSystem (LM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet attribut représente l'acteur System. </t>
+    <t>Cet attribut représente l'acteur System.</t>
   </si>
   <si>
     <t>ActorSystem.XCN1</t>
@@ -671,7 +673,7 @@
     <t>AuthorDocumentEntry.role</t>
   </si>
   <si>
-    <t>ette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
+    <t>cette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
   </si>
   <si>
     <t>AuthorDocumentEntry.specialty</t>
@@ -763,6 +765,9 @@
   </si>
   <si>
     <t>AuthorSubmissionSet.role</t>
+  </si>
+  <si>
+    <t>ette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
   </si>
   <si>
     <t>AuthorSubmissionSet.specialty</t>
@@ -1001,10 +1006,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée contient les codes, libellés et codes système représentant :  • un évènement documenté (acte, traitement, diagnostic, etc…), • une modalité d'acquisition (contexte imagerie), • une région anatomique (contexte imagerie). </t>
-  </si>
-  <si>
-    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  • un évènement documenté (acte, traitement, diagnostic, etc…), • une modalité d'acquisition (contexte imagerie), • une région anatomique (contexte imagerie).</t>
+    <t xml:space="preserve">Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie). </t>
+  </si>
+  <si>
+    <t>Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie).</t>
   </si>
   <si>
     <t>DocumentEntry.format</t>
@@ -1211,9 +1216,6 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/Identifiant</t>
   </si>
   <si>
-    <t xml:space="preserve"> Identifiant</t>
-  </si>
-  <si>
     <t>Identifiant de professionnel de santé, de patient, de SNR ou de système</t>
   </si>
   <si>
@@ -1225,9 +1227,6 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IdentifiantSysteme</t>
   </si>
   <si>
     <t xml:space="preserve">Identification d'un systeme
@@ -1398,9 +1397,6 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SNR</t>
   </si>
   <si>
-    <t xml:space="preserve"> SNR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identifiant interne de l’instance de la solution ayant produit le document au format OID </t>
   </si>
   <si>
@@ -1413,7 +1409,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SourcePatientId</t>
   </si>
   <si>
-    <t xml:space="preserve"> SourcePatientId (LM)</t>
+    <t>SourcePatientId (LM)</t>
   </si>
   <si>
     <t xml:space="preserve">Cette métadonnée contient l’identifiant secondaire du patient dans le système d’information du producteur (IPP) ou l’INS, s’il n’y a pas d’identifiant secondaire. Pour les documents d’expression personnelle du patient, cette métadonnée contient l’INS du patient, à savoir le même identifiant que patientId. </t>
@@ -1434,7 +1430,7 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve"> SourcePatientInfo (LM)</t>
+    <t>SourcePatientInfo (LM)</t>
   </si>
   <si>
     <t xml:space="preserve">Cette métadonnée contient les traits d’identité du patient concerné par le document, connus par le producteur du document. Les informations présentes dans la métadonnée sourcePatientInfo ne doivent en aucun cas être réutilisées pour calculer un identifiant, ni être mises à jour après la soumission du document. 
@@ -1511,9 +1507,6 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/StructIdNat</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> StructIdNat</t>
   </si>
   <si>
     <t xml:space="preserve">Identification nationale principale d’une structure propre aux SI de l'ANS et au CI-SIS 4. 
@@ -3247,7 +3240,7 @@
         <v>2</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="192">
@@ -3255,7 +3248,7 @@
         <v>4</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="193">
@@ -3271,7 +3264,7 @@
         <v>8</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="195">
@@ -3279,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196">
@@ -3333,7 +3326,7 @@
         <v>22</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203">
@@ -3369,7 +3362,7 @@
         <v>30</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="208">
@@ -3409,7 +3402,7 @@
         <v>2</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="213">
@@ -3417,7 +3410,7 @@
         <v>4</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="214">
@@ -3433,7 +3426,7 @@
         <v>8</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="216">
@@ -3441,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="217">
@@ -3495,7 +3488,7 @@
         <v>22</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="224">
@@ -3531,7 +3524,7 @@
         <v>30</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="229">
@@ -3571,7 +3564,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234">
@@ -3579,7 +3572,7 @@
         <v>4</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="235">
@@ -3595,7 +3588,7 @@
         <v>8</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="237">
@@ -3603,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238">
@@ -3657,7 +3650,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="245">
@@ -3693,7 +3686,7 @@
         <v>30</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="250">
@@ -3741,7 +3734,7 @@
         <v>4</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="256">
@@ -3765,7 +3758,7 @@
         <v>9</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>377</v>
+        <v>86</v>
       </c>
     </row>
     <row r="259">
@@ -3855,7 +3848,7 @@
         <v>30</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="271">
@@ -3927,7 +3920,7 @@
         <v>9</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="280">
@@ -3981,7 +3974,7 @@
         <v>22</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="287">
@@ -4009,7 +4002,7 @@
         <v>28</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="291">
@@ -4017,7 +4010,7 @@
         <v>30</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="292">
@@ -4025,7 +4018,7 @@
         <v>31</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="293">
@@ -4041,7 +4034,7 @@
         <v>35</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="295">
@@ -4057,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="297">
@@ -4065,7 +4058,7 @@
         <v>4</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="298">
@@ -4081,7 +4074,7 @@
         <v>8</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="300">
@@ -4089,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="301">
@@ -4143,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="308">
@@ -4179,7 +4172,7 @@
         <v>30</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="313">
@@ -4219,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="318">
@@ -4227,7 +4220,7 @@
         <v>4</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="319">
@@ -4243,7 +4236,7 @@
         <v>8</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="321">
@@ -4251,7 +4244,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="322">
@@ -4305,7 +4298,7 @@
         <v>22</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="329">
@@ -4341,7 +4334,7 @@
         <v>30</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="334">
@@ -4381,7 +4374,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="339">
@@ -4389,7 +4382,7 @@
         <v>4</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="340">
@@ -4405,7 +4398,7 @@
         <v>8</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="342">
@@ -4413,7 +4406,7 @@
         <v>9</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="343">
@@ -4467,7 +4460,7 @@
         <v>22</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="350">
@@ -4503,7 +4496,7 @@
         <v>30</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="355">
@@ -4543,7 +4536,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="360">
@@ -4551,7 +4544,7 @@
         <v>4</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="361">
@@ -4567,7 +4560,7 @@
         <v>8</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="363">
@@ -4575,7 +4568,7 @@
         <v>9</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="364">
@@ -4629,7 +4622,7 @@
         <v>22</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="371">
@@ -4665,7 +4658,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="376">
@@ -4705,7 +4698,7 @@
         <v>2</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="381">
@@ -4713,7 +4706,7 @@
         <v>4</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="382">
@@ -4729,7 +4722,7 @@
         <v>8</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="384">
@@ -4737,7 +4730,7 @@
         <v>9</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="385">
@@ -4791,7 +4784,7 @@
         <v>22</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="392">
@@ -4827,7 +4820,7 @@
         <v>30</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="397">
@@ -4867,7 +4860,7 @@
         <v>2</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="402">
@@ -4875,7 +4868,7 @@
         <v>4</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="403">
@@ -4891,7 +4884,7 @@
         <v>8</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="405">
@@ -4899,7 +4892,7 @@
         <v>9</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="406">
@@ -4953,7 +4946,7 @@
         <v>22</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="413">
@@ -4989,7 +4982,7 @@
         <v>30</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="418">
@@ -5029,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="423">
@@ -5037,7 +5030,7 @@
         <v>4</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="424">
@@ -5053,7 +5046,7 @@
         <v>8</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="426">
@@ -5061,7 +5054,7 @@
         <v>9</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="427">
@@ -5115,7 +5108,7 @@
         <v>22</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="434">
@@ -5151,7 +5144,7 @@
         <v>30</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="439">
@@ -5191,7 +5184,7 @@
         <v>2</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="444">
@@ -5199,7 +5192,7 @@
         <v>4</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="445">
@@ -5215,7 +5208,7 @@
         <v>8</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="447">
@@ -5223,7 +5216,7 @@
         <v>9</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="448">
@@ -5277,7 +5270,7 @@
         <v>22</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="455">
@@ -5313,7 +5306,7 @@
         <v>30</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="460">
@@ -13251,7 +13244,7 @@
         <v>192</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>194</v>
@@ -13323,10 +13316,10 @@
         <v>231</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -13421,13 +13414,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -13453,10 +13446,10 @@
         <v>76</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -13524,13 +13517,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -13553,13 +13546,13 @@
         <v>73</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -13610,7 +13603,7 @@
         <v>73</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>79</v>
@@ -13627,13 +13620,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -13656,13 +13649,13 @@
         <v>73</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
@@ -13713,7 +13706,7 @@
         <v>73</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>79</v>
@@ -13730,13 +13723,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -13762,10 +13755,10 @@
         <v>89</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -13816,7 +13809,7 @@
         <v>73</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>79</v>
@@ -13833,13 +13826,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -13865,10 +13858,10 @@
         <v>192</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -13899,7 +13892,7 @@
       </c>
       <c r="Z83" s="2"/>
       <c r="AA83" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>73</v>
@@ -13917,7 +13910,7 @@
         <v>73</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>79</v>
@@ -13934,13 +13927,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -13966,10 +13959,10 @@
         <v>89</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -14020,7 +14013,7 @@
         <v>73</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>79</v>
@@ -14037,13 +14030,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -14066,13 +14059,13 @@
         <v>73</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -14123,7 +14116,7 @@
         <v>73</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>79</v>
@@ -14140,13 +14133,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -14172,10 +14165,10 @@
         <v>89</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -14226,7 +14219,7 @@
         <v>73</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>79</v>
@@ -14243,13 +14236,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -14272,13 +14265,13 @@
         <v>73</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -14329,7 +14322,7 @@
         <v>73</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>79</v>
@@ -14346,13 +14339,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -14375,13 +14368,13 @@
         <v>73</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -14432,7 +14425,7 @@
         <v>73</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>79</v>
@@ -14449,13 +14442,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -14478,13 +14471,13 @@
         <v>73</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -14535,7 +14528,7 @@
         <v>73</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>79</v>
@@ -14552,13 +14545,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -14581,13 +14574,13 @@
         <v>73</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -14638,7 +14631,7 @@
         <v>73</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>79</v>
@@ -14655,13 +14648,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -14684,13 +14677,13 @@
         <v>73</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -14741,7 +14734,7 @@
         <v>73</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>74</v>
@@ -14758,13 +14751,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -14787,13 +14780,13 @@
         <v>73</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -14844,7 +14837,7 @@
         <v>73</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>79</v>
@@ -14861,13 +14854,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -14890,13 +14883,13 @@
         <v>73</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -14947,7 +14940,7 @@
         <v>73</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>79</v>
@@ -14964,13 +14957,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -14996,10 +14989,10 @@
         <v>89</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -15050,7 +15043,7 @@
         <v>73</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>79</v>
@@ -15067,13 +15060,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -15099,10 +15092,10 @@
         <v>89</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -15153,7 +15146,7 @@
         <v>73</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>79</v>
@@ -15170,13 +15163,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -15202,10 +15195,10 @@
         <v>89</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -15256,7 +15249,7 @@
         <v>73</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>74</v>
@@ -15273,13 +15266,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -15302,13 +15295,13 @@
         <v>73</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
@@ -15359,7 +15352,7 @@
         <v>73</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>79</v>
@@ -15376,13 +15369,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -15405,13 +15398,13 @@
         <v>73</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -15462,7 +15455,7 @@
         <v>73</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>79</v>
@@ -15479,13 +15472,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -15511,10 +15504,10 @@
         <v>192</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -15545,7 +15538,7 @@
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>73</v>
@@ -15563,7 +15556,7 @@
         <v>73</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>79</v>
@@ -15580,13 +15573,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -15597,7 +15590,7 @@
         <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>73</v>
@@ -15612,10 +15605,10 @@
         <v>192</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -15646,7 +15639,7 @@
       </c>
       <c r="Z100" s="2"/>
       <c r="AA100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>73</v>
@@ -15664,13 +15657,13 @@
         <v>73</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>73</v>
@@ -15681,13 +15674,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -15710,13 +15703,13 @@
         <v>73</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -15767,7 +15760,7 @@
         <v>73</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>74</v>
@@ -15784,13 +15777,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -15816,10 +15809,10 @@
         <v>192</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -15850,7 +15843,7 @@
       </c>
       <c r="Z102" s="2"/>
       <c r="AA102" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>73</v>
@@ -15868,7 +15861,7 @@
         <v>73</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>79</v>
@@ -15885,13 +15878,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -15917,10 +15910,10 @@
         <v>192</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
@@ -15951,7 +15944,7 @@
       </c>
       <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>73</v>
@@ -15969,7 +15962,7 @@
         <v>73</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>79</v>
@@ -15986,13 +15979,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -16018,10 +16011,10 @@
         <v>192</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -16052,7 +16045,7 @@
       </c>
       <c r="Z104" s="2"/>
       <c r="AA104" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>73</v>
@@ -16070,7 +16063,7 @@
         <v>73</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>79</v>
@@ -16087,13 +16080,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -16119,10 +16112,10 @@
         <v>192</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -16153,7 +16146,7 @@
       </c>
       <c r="Z105" s="2"/>
       <c r="AA105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>73</v>
@@ -16171,7 +16164,7 @@
         <v>73</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>79</v>
@@ -16188,13 +16181,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -16220,10 +16213,10 @@
         <v>89</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -16274,7 +16267,7 @@
         <v>73</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>74</v>
@@ -16291,13 +16284,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -16320,13 +16313,13 @@
         <v>73</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -16377,7 +16370,7 @@
         <v>73</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>74</v>
@@ -16394,13 +16387,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -16423,13 +16416,13 @@
         <v>73</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
@@ -16480,7 +16473,7 @@
         <v>73</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>79</v>
@@ -16497,13 +16490,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -16529,10 +16522,10 @@
         <v>98</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -16583,7 +16576,7 @@
         <v>73</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>74</v>
@@ -16600,13 +16593,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -16629,13 +16622,13 @@
         <v>73</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -16686,7 +16679,7 @@
         <v>73</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>79</v>
@@ -16703,13 +16696,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16732,13 +16725,13 @@
         <v>73</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -16789,7 +16782,7 @@
         <v>73</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>79</v>
@@ -16806,13 +16799,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16872,25 +16865,25 @@
       </c>
       <c r="Z112" s="2"/>
       <c r="AA112" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG112" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>79</v>
@@ -16907,13 +16900,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -16936,13 +16929,13 @@
         <v>73</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -16993,7 +16986,7 @@
         <v>73</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>74</v>
@@ -17010,13 +17003,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -17042,10 +17035,10 @@
         <v>76</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
@@ -17113,13 +17106,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -17145,10 +17138,10 @@
         <v>192</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
@@ -17199,7 +17192,7 @@
         <v>73</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>79</v>
@@ -17216,13 +17209,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -17248,10 +17241,10 @@
         <v>76</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -17319,13 +17312,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -17351,10 +17344,10 @@
         <v>192</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -17385,7 +17378,7 @@
       </c>
       <c r="Z117" s="2"/>
       <c r="AA117" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AB117" t="s" s="2">
         <v>73</v>
@@ -17403,7 +17396,7 @@
         <v>73</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>79</v>
@@ -17420,13 +17413,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -17452,10 +17445,10 @@
         <v>192</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -17506,7 +17499,7 @@
         <v>73</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>79</v>
@@ -17523,13 +17516,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -17555,10 +17548,10 @@
         <v>89</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -17609,7 +17602,7 @@
         <v>73</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>74</v>
@@ -17626,13 +17619,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -17655,13 +17648,13 @@
         <v>73</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -17712,7 +17705,7 @@
         <v>73</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>79</v>
@@ -17729,13 +17722,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -17758,13 +17751,13 @@
         <v>73</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -17815,7 +17808,7 @@
         <v>73</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>79</v>
@@ -17832,13 +17825,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17861,13 +17854,13 @@
         <v>73</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -17918,7 +17911,7 @@
         <v>73</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>79</v>
@@ -17935,13 +17928,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -17967,10 +17960,10 @@
         <v>89</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -18021,7 +18014,7 @@
         <v>73</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>79</v>
@@ -18038,13 +18031,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -18067,13 +18060,13 @@
         <v>73</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -18124,7 +18117,7 @@
         <v>73</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>79</v>
@@ -18141,13 +18134,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -18170,13 +18163,13 @@
         <v>73</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -18227,7 +18220,7 @@
         <v>73</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>74</v>
@@ -18244,13 +18237,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -18273,13 +18266,13 @@
         <v>73</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -18330,7 +18323,7 @@
         <v>73</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>79</v>
@@ -18347,13 +18340,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -18376,13 +18369,13 @@
         <v>73</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -18433,7 +18426,7 @@
         <v>73</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>74</v>
@@ -18482,7 +18475,7 @@
         <v>76</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>377</v>
+        <v>86</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>378</v>
@@ -18659,10 +18652,10 @@
         <v>380</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -18688,13 +18681,13 @@
         <v>76</v>
       </c>
       <c r="M130" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -18744,7 +18737,7 @@
         <v>73</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>74</v>
@@ -18756,7 +18749,7 @@
         <v>73</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131">
@@ -18764,10 +18757,10 @@
         <v>380</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18793,10 +18786,10 @@
         <v>89</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -18847,7 +18840,7 @@
         <v>73</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>74</v>
@@ -18867,14 +18860,14 @@
         <v>380</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" t="s" s="2">
@@ -18893,16 +18886,16 @@
         <v>73</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N132" t="s" s="2">
+      <c r="O132" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -18952,7 +18945,7 @@
         <v>73</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>74</v>
@@ -18964,7 +18957,7 @@
         <v>73</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133">
@@ -18972,10 +18965,10 @@
         <v>380</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -19001,10 +18994,10 @@
         <v>89</v>
       </c>
       <c r="M133" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -19028,7 +19021,7 @@
         <v>73</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y133" t="s" s="2">
         <v>73</v>
@@ -19055,7 +19048,7 @@
         <v>73</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>74</v>
@@ -19072,13 +19065,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -19104,10 +19097,10 @@
         <v>76</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -19175,13 +19168,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -19207,10 +19200,10 @@
         <v>89</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -19261,7 +19254,7 @@
         <v>73</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>79</v>
@@ -19278,13 +19271,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -19310,10 +19303,10 @@
         <v>76</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -19381,13 +19374,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -19413,10 +19406,10 @@
         <v>89</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
@@ -19467,30 +19460,30 @@
         <v>73</v>
       </c>
       <c r="AG137" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK137" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -19516,10 +19509,10 @@
         <v>76</v>
       </c>
       <c r="M138" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N138" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -19587,13 +19580,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -19616,13 +19609,13 @@
         <v>73</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
@@ -19673,7 +19666,7 @@
         <v>73</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>79</v>
@@ -19690,13 +19683,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19722,10 +19715,10 @@
         <v>89</v>
       </c>
       <c r="M140" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N140" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -19776,7 +19769,7 @@
         <v>73</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>79</v>
@@ -19793,13 +19786,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19825,10 +19818,10 @@
         <v>89</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
@@ -19879,7 +19872,7 @@
         <v>73</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>79</v>
@@ -19896,13 +19889,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19928,10 +19921,10 @@
         <v>76</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -19999,13 +19992,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -20031,10 +20024,10 @@
         <v>89</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -20085,7 +20078,7 @@
         <v>73</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>79</v>
@@ -20102,13 +20095,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -20134,10 +20127,10 @@
         <v>76</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -20205,13 +20198,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -20234,13 +20227,13 @@
         <v>73</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -20291,7 +20284,7 @@
         <v>73</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>79</v>
@@ -20308,13 +20301,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -20340,10 +20333,10 @@
         <v>89</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -20394,7 +20387,7 @@
         <v>73</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>79</v>
@@ -20411,13 +20404,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -20443,10 +20436,10 @@
         <v>89</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
@@ -20497,7 +20490,7 @@
         <v>73</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>79</v>
@@ -20514,13 +20507,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -20546,10 +20539,10 @@
         <v>76</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -20617,13 +20610,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -20646,13 +20639,13 @@
         <v>73</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -20703,7 +20696,7 @@
         <v>73</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>74</v>
@@ -20720,13 +20713,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20752,10 +20745,10 @@
         <v>89</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -20806,7 +20799,7 @@
         <v>73</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>79</v>
@@ -20823,13 +20816,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20855,10 +20848,10 @@
         <v>89</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
@@ -20909,7 +20902,7 @@
         <v>73</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>74</v>
@@ -20926,13 +20919,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20958,10 +20951,10 @@
         <v>89</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -21012,7 +21005,7 @@
         <v>73</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>74</v>
@@ -21029,13 +21022,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -21061,10 +21054,10 @@
         <v>89</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -21115,7 +21108,7 @@
         <v>73</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>74</v>
@@ -21132,13 +21125,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -21164,10 +21157,10 @@
         <v>89</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -21218,7 +21211,7 @@
         <v>73</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>74</v>
@@ -21235,13 +21228,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -21267,10 +21260,10 @@
         <v>89</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
@@ -21321,7 +21314,7 @@
         <v>73</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>74</v>
@@ -21338,13 +21331,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -21370,10 +21363,10 @@
         <v>89</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
@@ -21424,7 +21417,7 @@
         <v>73</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>74</v>
@@ -21441,13 +21434,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -21473,10 +21466,10 @@
         <v>89</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -21527,7 +21520,7 @@
         <v>73</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>74</v>
@@ -21544,13 +21537,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -21576,10 +21569,10 @@
         <v>89</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
@@ -21630,7 +21623,7 @@
         <v>73</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>74</v>
@@ -21647,13 +21640,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21679,10 +21672,10 @@
         <v>89</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
@@ -21733,7 +21726,7 @@
         <v>73</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>74</v>
@@ -21750,13 +21743,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21782,10 +21775,10 @@
         <v>76</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -21853,13 +21846,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21885,10 +21878,10 @@
         <v>89</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -21939,7 +21932,7 @@
         <v>73</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>79</v>
@@ -21956,13 +21949,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21988,10 +21981,10 @@
         <v>76</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -22059,13 +22052,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -22088,13 +22081,13 @@
         <v>73</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -22145,7 +22138,7 @@
         <v>73</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>79</v>
@@ -22162,13 +22155,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -22194,10 +22187,10 @@
         <v>112</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -22212,7 +22205,7 @@
         <v>73</v>
       </c>
       <c r="U164" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="V164" t="s" s="2">
         <v>73</v>
@@ -22224,11 +22217,11 @@
         <v>73</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="Z164" s="2"/>
       <c r="AA164" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AB164" t="s" s="2">
         <v>73</v>
@@ -22246,7 +22239,7 @@
         <v>73</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>79</v>
@@ -22263,13 +22256,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -22292,13 +22285,13 @@
         <v>73</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
@@ -22349,7 +22342,7 @@
         <v>73</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>79</v>
@@ -22366,13 +22359,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -22398,10 +22391,10 @@
         <v>89</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -22452,7 +22445,7 @@
         <v>73</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>74</v>
@@ -22469,13 +22462,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -22501,10 +22494,10 @@
         <v>89</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -22555,7 +22548,7 @@
         <v>73</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>74</v>
@@ -22572,13 +22565,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -22601,13 +22594,13 @@
         <v>73</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -22658,7 +22651,7 @@
         <v>73</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>79</v>
@@ -22675,13 +22668,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22704,13 +22697,13 @@
         <v>73</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
@@ -22761,7 +22754,7 @@
         <v>73</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>79</v>
@@ -22778,13 +22771,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22807,13 +22800,13 @@
         <v>73</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -22864,7 +22857,7 @@
         <v>73</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>79</v>
@@ -22881,13 +22874,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -22913,10 +22906,10 @@
         <v>192</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -22947,7 +22940,7 @@
       </c>
       <c r="Z171" s="2"/>
       <c r="AA171" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AB171" t="s" s="2">
         <v>73</v>
@@ -22965,7 +22958,7 @@
         <v>73</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>79</v>
@@ -22982,13 +22975,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -23011,13 +23004,13 @@
         <v>73</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -23068,7 +23061,7 @@
         <v>73</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>79</v>
@@ -23085,13 +23078,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -23114,13 +23107,13 @@
         <v>73</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
@@ -23171,7 +23164,7 @@
         <v>73</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>74</v>
@@ -23188,13 +23181,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -23220,10 +23213,10 @@
         <v>89</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -23274,7 +23267,7 @@
         <v>73</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>74</v>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6451" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6451" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -113,7 +113,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -532,7 +532,7 @@
     <t>ActorSystem.XCN1.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme}
+    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme|0.1.0}
 </t>
   </si>
   <si>
@@ -561,6 +561,9 @@
   </si>
   <si>
     <t>ActorXDS</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/ActorXDS</t>
   </si>
   <si>
     <t>ActorXDS (LM)</t>
@@ -570,7 +573,7 @@
 XCN de HL7 v2.5</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
   </si>
   <si>
     <t>Author</t>
@@ -625,7 +628,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS|20250523120000</t>
   </si>
   <si>
     <t>Author.specialty</t>
@@ -637,7 +640,7 @@
     <t>**AutorSpecialty**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260505120000</t>
   </si>
   <si>
     <t>AuthorDocumentEntry</t>
@@ -658,6 +661,9 @@
 -  Un SNR (Service Numérique Référencé), </t>
   </si>
   <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/Author|0.1.0</t>
+  </si>
+  <si>
     <t>AuthorDocumentEntry.institution</t>
   </si>
   <si>
@@ -823,7 +829,7 @@
     <t>**Availability Status**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J52-AvailabilityStatus-CISIS/FHIR/JDV-J52-AvailabilityStatus-CISIS|20200424120000</t>
   </si>
   <si>
     <t>DocumentEntry.hash</t>
@@ -981,7 +987,7 @@
 - Source : En fonction de l’interface fournie (ex. paramétrage fixe ou choix dans un menu déroulant).</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J06-XdsClassCode-CISIS/FHIR/JDV-J06-XdsClassCode-CISIS|20230922120000</t>
   </si>
   <si>
     <t>DocumentEntry.confidentiality</t>
@@ -996,7 +1002,7 @@
     <t>**Confidentiality Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J58-ConfidentialityCode-DMP/FHIR/JDV-J58-ConfidentialityCode-DMP</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J58-ConfidentialityCode-DMP/FHIR/JDV-J58-ConfidentialityCode-DMP|20200424120000</t>
   </si>
   <si>
     <t>DocumentEntry.eventCodeList</t>
@@ -1021,7 +1027,7 @@
     <t>**Format Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20251029120000</t>
   </si>
   <si>
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
@@ -1033,7 +1039,7 @@
     <t>Healthcare Facility Type Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J02-XdsHealthcareFacilityTypeCode-CISIS/FHIR/JDV-J02-XdsHealthcareFacilityTypeCode-CISIS|20260223120000</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSetting</t>
@@ -1045,7 +1051,7 @@
     <t>**Practice Setting**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J04-XdsPracticeSettingCode-CISIS/FHIR/JDV-J04-XdsPracticeSettingCode-CISIS|20240927120000</t>
   </si>
   <si>
     <t>DocumentEntry.type</t>
@@ -1057,7 +1063,7 @@
     <t>**Type Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260601120000</t>
   </si>
   <si>
     <t>DocumentEntry.documentAvailability</t>
@@ -1087,7 +1093,7 @@
     <t>DocumentEntry.referenceIdList.CX1</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {elementdefinition-identifier}
+    <t xml:space="preserve">Extension {elementdefinition-identifier|5.3.0}
 </t>
   </si>
   <si>
@@ -1103,7 +1109,7 @@
     <t>DocumentEntry.referenceIdList.CX5</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J197-XdsTypesIdentifiantsReferenceId-CISIS/FHIR/JDV-J197-XdsTypesIdentifiantsReferenceId-CISIS|20220624120000</t>
   </si>
   <si>
     <t>DocumentEntry.version</t>
@@ -1220,7 +1226,7 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/PSIdNat
-https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/MatriculeINShttps://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SNRstring {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme}</t>
+https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/MatriculeINShttps://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SNRstring {https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/IdentifiantSysteme|0.1.0}</t>
   </si>
   <si>
     <t>IdentifiantSysteme</t>
@@ -1245,7 +1251,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/string</t>
+    <t>http://hl7.org/fhir/StructureDefinition/string|4.0.1</t>
   </si>
   <si>
     <t>constraint</t>
@@ -1606,7 +1612,7 @@
     <t>**Submission Set**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS|20260223120000</t>
   </si>
   <si>
     <t>SubmissionSet.author</t>
@@ -2438,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>32</v>
+        <v>179</v>
       </c>
     </row>
     <row r="88">
@@ -2462,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91">
@@ -2516,7 +2522,7 @@
         <v>22</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98">
@@ -2552,7 +2558,7 @@
         <v>30</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>32</v>
+        <v>179</v>
       </c>
     </row>
     <row r="103">
@@ -2560,7 +2566,7 @@
         <v>31</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104">
@@ -2592,7 +2598,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="108">
@@ -2600,7 +2606,7 @@
         <v>4</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109">
@@ -2616,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="111">
@@ -2624,7 +2630,7 @@
         <v>9</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="112">
@@ -2678,7 +2684,7 @@
         <v>22</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="119">
@@ -2714,7 +2720,7 @@
         <v>30</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124">
@@ -2722,7 +2728,7 @@
         <v>31</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125">
@@ -2754,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129">
@@ -2762,7 +2768,7 @@
         <v>4</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130">
@@ -2778,7 +2784,7 @@
         <v>8</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132">
@@ -2786,7 +2792,7 @@
         <v>9</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="133">
@@ -2840,7 +2846,7 @@
         <v>22</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="140">
@@ -2876,7 +2882,7 @@
         <v>30</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="145">
@@ -2884,7 +2890,7 @@
         <v>31</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>183</v>
+        <v>206</v>
       </c>
     </row>
     <row r="146">
@@ -2916,7 +2922,7 @@
         <v>2</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="150">
@@ -2924,7 +2930,7 @@
         <v>4</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="151">
@@ -2940,7 +2946,7 @@
         <v>8</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="153">
@@ -2948,7 +2954,7 @@
         <v>9</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="154">
@@ -3002,7 +3008,7 @@
         <v>22</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="161">
@@ -3038,7 +3044,7 @@
         <v>30</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166">
@@ -3046,7 +3052,7 @@
         <v>31</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="167">
@@ -3078,7 +3084,7 @@
         <v>2</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="171">
@@ -3086,7 +3092,7 @@
         <v>4</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="172">
@@ -3102,7 +3108,7 @@
         <v>8</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="174">
@@ -3110,7 +3116,7 @@
         <v>9</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="175">
@@ -3164,7 +3170,7 @@
         <v>22</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="182">
@@ -3200,7 +3206,7 @@
         <v>30</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="187">
@@ -3208,7 +3214,7 @@
         <v>31</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>183</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188">
@@ -3240,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192">
@@ -3248,7 +3254,7 @@
         <v>4</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="193">
@@ -3264,7 +3270,7 @@
         <v>8</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195">
@@ -3272,7 +3278,7 @@
         <v>9</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="196">
@@ -3326,7 +3332,7 @@
         <v>22</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="203">
@@ -3362,7 +3368,7 @@
         <v>30</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="208">
@@ -3370,7 +3376,7 @@
         <v>31</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="209">
@@ -3402,7 +3408,7 @@
         <v>2</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="213">
@@ -3410,7 +3416,7 @@
         <v>4</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="214">
@@ -3426,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="216">
@@ -3434,7 +3440,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="217">
@@ -3488,7 +3494,7 @@
         <v>22</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="224">
@@ -3524,7 +3530,7 @@
         <v>30</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="229">
@@ -3532,7 +3538,7 @@
         <v>31</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="230">
@@ -3564,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="234">
@@ -3572,7 +3578,7 @@
         <v>4</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="235">
@@ -3588,7 +3594,7 @@
         <v>8</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="237">
@@ -3596,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="238">
@@ -3650,7 +3656,7 @@
         <v>22</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="245">
@@ -3686,7 +3692,7 @@
         <v>30</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="250">
@@ -3694,7 +3700,7 @@
         <v>31</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="251">
@@ -3734,7 +3740,7 @@
         <v>4</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="256">
@@ -3812,7 +3818,7 @@
         <v>22</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="266">
@@ -3848,7 +3854,7 @@
         <v>30</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="271">
@@ -3856,7 +3862,7 @@
         <v>31</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="272">
@@ -3888,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="276">
@@ -3896,7 +3902,7 @@
         <v>4</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="277">
@@ -3912,7 +3918,7 @@
         <v>8</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="279">
@@ -3920,7 +3926,7 @@
         <v>9</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="280">
@@ -3974,7 +3980,7 @@
         <v>22</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="287">
@@ -4002,7 +4008,7 @@
         <v>28</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="291">
@@ -4010,7 +4016,7 @@
         <v>30</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="292">
@@ -4018,7 +4024,7 @@
         <v>31</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="293">
@@ -4034,7 +4040,7 @@
         <v>35</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="295">
@@ -4050,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="297">
@@ -4058,7 +4064,7 @@
         <v>4</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="298">
@@ -4074,7 +4080,7 @@
         <v>8</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="300">
@@ -4082,7 +4088,7 @@
         <v>9</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="301">
@@ -4136,7 +4142,7 @@
         <v>22</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="308">
@@ -4172,7 +4178,7 @@
         <v>30</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="313">
@@ -4180,7 +4186,7 @@
         <v>31</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="314">
@@ -4212,7 +4218,7 @@
         <v>2</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="318">
@@ -4220,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="319">
@@ -4236,7 +4242,7 @@
         <v>8</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="321">
@@ -4244,7 +4250,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="322">
@@ -4298,7 +4304,7 @@
         <v>22</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="329">
@@ -4334,7 +4340,7 @@
         <v>30</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="334">
@@ -4342,7 +4348,7 @@
         <v>31</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="335">
@@ -4374,7 +4380,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="339">
@@ -4382,7 +4388,7 @@
         <v>4</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="340">
@@ -4398,7 +4404,7 @@
         <v>8</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="342">
@@ -4406,7 +4412,7 @@
         <v>9</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="343">
@@ -4460,7 +4466,7 @@
         <v>22</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="350">
@@ -4496,7 +4502,7 @@
         <v>30</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="355">
@@ -4504,7 +4510,7 @@
         <v>31</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="356">
@@ -4536,7 +4542,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="360">
@@ -4544,7 +4550,7 @@
         <v>4</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="361">
@@ -4560,7 +4566,7 @@
         <v>8</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="363">
@@ -4568,7 +4574,7 @@
         <v>9</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="364">
@@ -4622,7 +4628,7 @@
         <v>22</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="371">
@@ -4658,7 +4664,7 @@
         <v>30</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="376">
@@ -4666,7 +4672,7 @@
         <v>31</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="377">
@@ -4698,7 +4704,7 @@
         <v>2</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="381">
@@ -4706,7 +4712,7 @@
         <v>4</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="382">
@@ -4722,7 +4728,7 @@
         <v>8</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="384">
@@ -4730,7 +4736,7 @@
         <v>9</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="385">
@@ -4784,7 +4790,7 @@
         <v>22</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="392">
@@ -4820,7 +4826,7 @@
         <v>30</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="397">
@@ -4828,7 +4834,7 @@
         <v>31</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="398">
@@ -4860,7 +4866,7 @@
         <v>2</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="402">
@@ -4868,7 +4874,7 @@
         <v>4</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="403">
@@ -4884,7 +4890,7 @@
         <v>8</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="405">
@@ -4892,7 +4898,7 @@
         <v>9</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="406">
@@ -4946,7 +4952,7 @@
         <v>22</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="413">
@@ -4982,7 +4988,7 @@
         <v>30</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="418">
@@ -4990,7 +4996,7 @@
         <v>31</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="419">
@@ -5022,7 +5028,7 @@
         <v>2</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="423">
@@ -5030,7 +5036,7 @@
         <v>4</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="424">
@@ -5046,7 +5052,7 @@
         <v>8</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="426">
@@ -5054,7 +5060,7 @@
         <v>9</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="427">
@@ -5108,7 +5114,7 @@
         <v>22</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="434">
@@ -5144,7 +5150,7 @@
         <v>30</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="439">
@@ -5152,7 +5158,7 @@
         <v>31</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="440">
@@ -5184,7 +5190,7 @@
         <v>2</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="444">
@@ -5192,7 +5198,7 @@
         <v>4</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="445">
@@ -5208,7 +5214,7 @@
         <v>8</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="447">
@@ -5216,7 +5222,7 @@
         <v>9</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="448">
@@ -5270,7 +5276,7 @@
         <v>22</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="455">
@@ -5306,7 +5312,7 @@
         <v>30</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="460">
@@ -5314,7 +5320,7 @@
         <v>31</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="461">
@@ -5369,7 +5375,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="106.83203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="121.359375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.65625" customWidth="true" bestFit="true"/>
@@ -10059,10 +10065,10 @@
         <v>76</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -11057,13 +11063,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -11089,10 +11095,10 @@
         <v>76</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -11160,13 +11166,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -11189,13 +11195,13 @@
         <v>73</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -11246,7 +11252,7 @@
         <v>73</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>74</v>
@@ -11263,13 +11269,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -11292,13 +11298,13 @@
         <v>73</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -11349,7 +11355,7 @@
         <v>73</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>79</v>
@@ -11366,13 +11372,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -11395,13 +11401,13 @@
         <v>73</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -11428,11 +11434,11 @@
         <v>73</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z59" s="2"/>
       <c r="AA59" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AB59" t="s" s="2">
         <v>73</v>
@@ -11450,7 +11456,7 @@
         <v>73</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>74</v>
@@ -11467,13 +11473,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -11496,13 +11502,13 @@
         <v>73</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -11529,11 +11535,11 @@
         <v>73</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z60" s="2"/>
       <c r="AA60" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AB60" t="s" s="2">
         <v>73</v>
@@ -11551,7 +11557,7 @@
         <v>73</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>74</v>
@@ -11568,13 +11574,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -11600,10 +11606,10 @@
         <v>76</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -11671,13 +11677,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -11700,13 +11706,13 @@
         <v>73</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -11757,7 +11763,7 @@
         <v>73</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>74</v>
@@ -11774,13 +11780,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -11803,13 +11809,13 @@
         <v>73</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
@@ -11860,7 +11866,7 @@
         <v>73</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>79</v>
@@ -11877,13 +11883,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -11906,13 +11912,13 @@
         <v>73</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -11939,11 +11945,11 @@
         <v>73</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z64" s="2"/>
       <c r="AA64" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AB64" t="s" s="2">
         <v>73</v>
@@ -11961,7 +11967,7 @@
         <v>73</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>74</v>
@@ -11978,13 +11984,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -12007,13 +12013,13 @@
         <v>73</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -12040,11 +12046,11 @@
         <v>73</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z65" s="2"/>
       <c r="AA65" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>73</v>
@@ -12062,7 +12068,7 @@
         <v>73</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>74</v>
@@ -12079,13 +12085,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -12111,10 +12117,10 @@
         <v>76</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -12182,13 +12188,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -12214,10 +12220,10 @@
         <v>89</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
@@ -12232,43 +12238,43 @@
         <v>73</v>
       </c>
       <c r="U67" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG67" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>79</v>
@@ -12285,13 +12291,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -12317,10 +12323,10 @@
         <v>98</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
@@ -12371,7 +12377,7 @@
         <v>73</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>79</v>
@@ -12388,13 +12394,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -12474,7 +12480,7 @@
         <v>73</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>74</v>
@@ -12491,13 +12497,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -12541,7 +12547,7 @@
         <v>73</v>
       </c>
       <c r="U70" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="V70" t="s" s="2">
         <v>73</v>
@@ -12577,7 +12583,7 @@
         <v>73</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>79</v>
@@ -12594,13 +12600,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -12680,7 +12686,7 @@
         <v>73</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>79</v>
@@ -12697,13 +12703,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -12747,7 +12753,7 @@
         <v>73</v>
       </c>
       <c r="U72" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="V72" t="s" s="2">
         <v>73</v>
@@ -12783,7 +12789,7 @@
         <v>73</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>79</v>
@@ -12800,13 +12806,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -12829,13 +12835,13 @@
         <v>73</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
@@ -12886,7 +12892,7 @@
         <v>73</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>79</v>
@@ -12903,13 +12909,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -12935,10 +12941,10 @@
         <v>76</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -13006,13 +13012,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -13035,13 +13041,13 @@
         <v>73</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -13092,7 +13098,7 @@
         <v>73</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>74</v>
@@ -13109,13 +13115,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -13138,13 +13144,13 @@
         <v>73</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
@@ -13195,7 +13201,7 @@
         <v>73</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>79</v>
@@ -13212,13 +13218,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -13241,13 +13247,13 @@
         <v>73</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
@@ -13274,11 +13280,11 @@
         <v>73</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z77" s="2"/>
       <c r="AA77" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AB77" t="s" s="2">
         <v>73</v>
@@ -13296,7 +13302,7 @@
         <v>73</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>74</v>
@@ -13313,13 +13319,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -13342,13 +13348,13 @@
         <v>73</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -13375,11 +13381,11 @@
         <v>73</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z78" s="2"/>
       <c r="AA78" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>73</v>
@@ -13397,7 +13403,7 @@
         <v>73</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>74</v>
@@ -13414,13 +13420,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -13446,10 +13452,10 @@
         <v>76</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -13517,13 +13523,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -13546,13 +13552,13 @@
         <v>73</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -13603,7 +13609,7 @@
         <v>73</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>79</v>
@@ -13620,13 +13626,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -13649,13 +13655,13 @@
         <v>73</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
@@ -13706,7 +13712,7 @@
         <v>73</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>79</v>
@@ -13723,13 +13729,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -13755,10 +13761,10 @@
         <v>89</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -13809,7 +13815,7 @@
         <v>73</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>79</v>
@@ -13826,13 +13832,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -13855,13 +13861,13 @@
         <v>73</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -13888,11 +13894,11 @@
         <v>73</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z83" s="2"/>
       <c r="AA83" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>73</v>
@@ -13910,7 +13916,7 @@
         <v>73</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>79</v>
@@ -13927,13 +13933,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -13959,10 +13965,10 @@
         <v>89</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
@@ -14013,7 +14019,7 @@
         <v>73</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>79</v>
@@ -14030,13 +14036,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -14059,13 +14065,13 @@
         <v>73</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
@@ -14116,7 +14122,7 @@
         <v>73</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>79</v>
@@ -14133,13 +14139,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -14165,10 +14171,10 @@
         <v>89</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -14219,7 +14225,7 @@
         <v>73</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>79</v>
@@ -14236,13 +14242,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -14265,13 +14271,13 @@
         <v>73</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -14322,7 +14328,7 @@
         <v>73</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>79</v>
@@ -14339,13 +14345,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -14368,13 +14374,13 @@
         <v>73</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -14425,7 +14431,7 @@
         <v>73</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>79</v>
@@ -14442,13 +14448,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -14471,13 +14477,13 @@
         <v>73</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -14528,7 +14534,7 @@
         <v>73</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>79</v>
@@ -14545,13 +14551,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -14574,13 +14580,13 @@
         <v>73</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -14631,7 +14637,7 @@
         <v>73</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>79</v>
@@ -14648,13 +14654,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -14677,13 +14683,13 @@
         <v>73</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -14734,7 +14740,7 @@
         <v>73</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>74</v>
@@ -14751,13 +14757,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -14780,13 +14786,13 @@
         <v>73</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -14837,7 +14843,7 @@
         <v>73</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>79</v>
@@ -14854,13 +14860,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -14883,13 +14889,13 @@
         <v>73</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -14940,7 +14946,7 @@
         <v>73</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>79</v>
@@ -14957,13 +14963,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -14989,10 +14995,10 @@
         <v>89</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -15043,7 +15049,7 @@
         <v>73</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>79</v>
@@ -15060,13 +15066,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -15092,10 +15098,10 @@
         <v>89</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -15146,7 +15152,7 @@
         <v>73</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>79</v>
@@ -15163,13 +15169,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -15195,10 +15201,10 @@
         <v>89</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -15249,7 +15255,7 @@
         <v>73</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>74</v>
@@ -15266,13 +15272,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -15295,13 +15301,13 @@
         <v>73</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
@@ -15352,7 +15358,7 @@
         <v>73</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>79</v>
@@ -15369,13 +15375,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -15398,13 +15404,13 @@
         <v>73</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -15455,7 +15461,7 @@
         <v>73</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>79</v>
@@ -15472,13 +15478,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -15501,13 +15507,13 @@
         <v>73</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -15534,11 +15540,11 @@
         <v>73</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z99" s="2"/>
       <c r="AA99" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AB99" t="s" s="2">
         <v>73</v>
@@ -15556,7 +15562,7 @@
         <v>73</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>79</v>
@@ -15573,13 +15579,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -15590,7 +15596,7 @@
         <v>79</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>73</v>
@@ -15602,13 +15608,13 @@
         <v>73</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -15635,11 +15641,11 @@
         <v>73</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z100" s="2"/>
       <c r="AA100" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>73</v>
@@ -15657,13 +15663,13 @@
         <v>73</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>73</v>
@@ -15674,13 +15680,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -15703,13 +15709,13 @@
         <v>73</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
@@ -15760,7 +15766,7 @@
         <v>73</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>74</v>
@@ -15777,13 +15783,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -15806,13 +15812,13 @@
         <v>73</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -15839,11 +15845,11 @@
         <v>73</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z102" s="2"/>
       <c r="AA102" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB102" t="s" s="2">
         <v>73</v>
@@ -15861,7 +15867,7 @@
         <v>73</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>79</v>
@@ -15878,13 +15884,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -15907,13 +15913,13 @@
         <v>73</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
@@ -15940,11 +15946,11 @@
         <v>73</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z103" s="2"/>
       <c r="AA103" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AB103" t="s" s="2">
         <v>73</v>
@@ -15962,7 +15968,7 @@
         <v>73</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>79</v>
@@ -15979,13 +15985,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -16008,13 +16014,13 @@
         <v>73</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -16041,11 +16047,11 @@
         <v>73</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z104" s="2"/>
       <c r="AA104" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AB104" t="s" s="2">
         <v>73</v>
@@ -16063,7 +16069,7 @@
         <v>73</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>79</v>
@@ -16080,13 +16086,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -16109,13 +16115,13 @@
         <v>73</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -16142,11 +16148,11 @@
         <v>73</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z105" s="2"/>
       <c r="AA105" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>73</v>
@@ -16164,7 +16170,7 @@
         <v>73</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>79</v>
@@ -16181,13 +16187,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -16213,10 +16219,10 @@
         <v>89</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -16267,7 +16273,7 @@
         <v>73</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>74</v>
@@ -16284,13 +16290,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -16313,13 +16319,13 @@
         <v>73</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -16370,7 +16376,7 @@
         <v>73</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>74</v>
@@ -16387,13 +16393,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -16416,13 +16422,13 @@
         <v>73</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
@@ -16473,7 +16479,7 @@
         <v>73</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>79</v>
@@ -16490,13 +16496,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -16522,10 +16528,10 @@
         <v>98</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -16576,7 +16582,7 @@
         <v>73</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>74</v>
@@ -16593,13 +16599,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -16622,13 +16628,13 @@
         <v>73</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -16679,7 +16685,7 @@
         <v>73</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>79</v>
@@ -16696,13 +16702,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16725,13 +16731,13 @@
         <v>73</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -16782,7 +16788,7 @@
         <v>73</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>79</v>
@@ -16799,13 +16805,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16828,7 +16834,7 @@
         <v>73</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M112" t="s" s="2">
         <v>117</v>
@@ -16861,11 +16867,11 @@
         <v>73</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z112" s="2"/>
       <c r="AA112" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AB112" t="s" s="2">
         <v>73</v>
@@ -16883,7 +16889,7 @@
         <v>73</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>79</v>
@@ -16900,13 +16906,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -16929,13 +16935,13 @@
         <v>73</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -16986,7 +16992,7 @@
         <v>73</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>74</v>
@@ -17003,13 +17009,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -17035,10 +17041,10 @@
         <v>76</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
@@ -17106,13 +17112,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -17135,13 +17141,13 @@
         <v>73</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
@@ -17192,7 +17198,7 @@
         <v>73</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>79</v>
@@ -17209,13 +17215,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -17241,10 +17247,10 @@
         <v>76</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -17312,13 +17318,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -17341,13 +17347,13 @@
         <v>73</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -17374,11 +17380,11 @@
         <v>73</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z117" s="2"/>
       <c r="AA117" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AB117" t="s" s="2">
         <v>73</v>
@@ -17396,7 +17402,7 @@
         <v>73</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>79</v>
@@ -17413,13 +17419,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -17442,13 +17448,13 @@
         <v>73</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -17499,7 +17505,7 @@
         <v>73</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>79</v>
@@ -17516,13 +17522,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -17548,10 +17554,10 @@
         <v>89</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -17602,7 +17608,7 @@
         <v>73</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>74</v>
@@ -17619,13 +17625,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -17648,13 +17654,13 @@
         <v>73</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -17705,7 +17711,7 @@
         <v>73</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>79</v>
@@ -17722,13 +17728,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -17751,13 +17757,13 @@
         <v>73</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
@@ -17808,7 +17814,7 @@
         <v>73</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>79</v>
@@ -17825,13 +17831,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17854,13 +17860,13 @@
         <v>73</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -17911,7 +17917,7 @@
         <v>73</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>79</v>
@@ -17928,13 +17934,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -17960,10 +17966,10 @@
         <v>89</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
@@ -18014,7 +18020,7 @@
         <v>73</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>79</v>
@@ -18031,13 +18037,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -18060,13 +18066,13 @@
         <v>73</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -18117,7 +18123,7 @@
         <v>73</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>79</v>
@@ -18134,13 +18140,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -18163,13 +18169,13 @@
         <v>73</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -18220,7 +18226,7 @@
         <v>73</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>74</v>
@@ -18237,13 +18243,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -18266,13 +18272,13 @@
         <v>73</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -18323,7 +18329,7 @@
         <v>73</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>79</v>
@@ -18340,13 +18346,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -18369,13 +18375,13 @@
         <v>73</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -18426,7 +18432,7 @@
         <v>73</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>74</v>
@@ -18478,7 +18484,7 @@
         <v>86</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
@@ -18575,7 +18581,7 @@
         <v>73</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>86</v>
@@ -18649,13 +18655,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -18681,13 +18687,13 @@
         <v>76</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
@@ -18737,7 +18743,7 @@
         <v>73</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>74</v>
@@ -18749,18 +18755,18 @@
         <v>73</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18786,10 +18792,10 @@
         <v>89</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
@@ -18840,7 +18846,7 @@
         <v>73</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>74</v>
@@ -18857,17 +18863,17 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" t="s" s="2">
@@ -18886,16 +18892,16 @@
         <v>73</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P132" s="2"/>
       <c r="Q132" t="s" s="2">
@@ -18945,7 +18951,7 @@
         <v>73</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>74</v>
@@ -18957,18 +18963,18 @@
         <v>73</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -18994,10 +19000,10 @@
         <v>89</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -19021,7 +19027,7 @@
         <v>73</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y133" t="s" s="2">
         <v>73</v>
@@ -19048,7 +19054,7 @@
         <v>73</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>74</v>
@@ -19065,13 +19071,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -19097,10 +19103,10 @@
         <v>76</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
@@ -19168,13 +19174,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -19200,10 +19206,10 @@
         <v>89</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
@@ -19254,7 +19260,7 @@
         <v>73</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>79</v>
@@ -19271,13 +19277,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -19303,10 +19309,10 @@
         <v>76</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
@@ -19374,13 +19380,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -19406,10 +19412,10 @@
         <v>89</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
@@ -19460,7 +19466,7 @@
         <v>73</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>79</v>
@@ -19472,18 +19478,18 @@
         <v>73</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -19509,10 +19515,10 @@
         <v>76</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
@@ -19580,13 +19586,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -19609,13 +19615,13 @@
         <v>73</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
@@ -19666,7 +19672,7 @@
         <v>73</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>79</v>
@@ -19683,13 +19689,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19715,10 +19721,10 @@
         <v>89</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
@@ -19769,7 +19775,7 @@
         <v>73</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>79</v>
@@ -19786,13 +19792,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19818,10 +19824,10 @@
         <v>89</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
@@ -19872,7 +19878,7 @@
         <v>73</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>79</v>
@@ -19889,13 +19895,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19921,10 +19927,10 @@
         <v>76</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -19992,13 +19998,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -20024,10 +20030,10 @@
         <v>89</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
@@ -20078,7 +20084,7 @@
         <v>73</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>79</v>
@@ -20095,13 +20101,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -20127,10 +20133,10 @@
         <v>76</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
@@ -20198,13 +20204,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -20227,13 +20233,13 @@
         <v>73</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -20284,7 +20290,7 @@
         <v>73</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>79</v>
@@ -20301,13 +20307,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -20333,10 +20339,10 @@
         <v>89</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -20387,7 +20393,7 @@
         <v>73</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>79</v>
@@ -20404,13 +20410,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -20436,10 +20442,10 @@
         <v>89</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
@@ -20490,7 +20496,7 @@
         <v>73</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>79</v>
@@ -20507,13 +20513,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -20539,10 +20545,10 @@
         <v>76</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -20610,13 +20616,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -20639,13 +20645,13 @@
         <v>73</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
@@ -20696,7 +20702,7 @@
         <v>73</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>74</v>
@@ -20713,13 +20719,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20745,10 +20751,10 @@
         <v>89</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -20799,7 +20805,7 @@
         <v>73</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>79</v>
@@ -20816,13 +20822,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20848,10 +20854,10 @@
         <v>89</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
@@ -20902,7 +20908,7 @@
         <v>73</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>74</v>
@@ -20919,13 +20925,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20951,10 +20957,10 @@
         <v>89</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -21005,7 +21011,7 @@
         <v>73</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>74</v>
@@ -21022,13 +21028,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -21054,10 +21060,10 @@
         <v>89</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -21108,7 +21114,7 @@
         <v>73</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>74</v>
@@ -21125,13 +21131,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -21157,10 +21163,10 @@
         <v>89</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -21211,7 +21217,7 @@
         <v>73</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>74</v>
@@ -21228,13 +21234,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -21260,10 +21266,10 @@
         <v>89</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
@@ -21314,7 +21320,7 @@
         <v>73</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>74</v>
@@ -21331,13 +21337,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -21363,10 +21369,10 @@
         <v>89</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
@@ -21417,7 +21423,7 @@
         <v>73</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>74</v>
@@ -21434,13 +21440,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -21466,10 +21472,10 @@
         <v>89</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
@@ -21520,7 +21526,7 @@
         <v>73</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>74</v>
@@ -21537,13 +21543,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -21569,10 +21575,10 @@
         <v>89</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
@@ -21623,7 +21629,7 @@
         <v>73</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>74</v>
@@ -21640,13 +21646,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21672,10 +21678,10 @@
         <v>89</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
@@ -21726,7 +21732,7 @@
         <v>73</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>74</v>
@@ -21743,13 +21749,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21775,10 +21781,10 @@
         <v>76</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -21846,13 +21852,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21878,10 +21884,10 @@
         <v>89</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -21932,7 +21938,7 @@
         <v>73</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>79</v>
@@ -21949,13 +21955,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21981,10 +21987,10 @@
         <v>76</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -22052,13 +22058,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -22081,13 +22087,13 @@
         <v>73</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -22138,7 +22144,7 @@
         <v>73</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>79</v>
@@ -22155,13 +22161,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -22187,10 +22193,10 @@
         <v>112</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -22205,7 +22211,7 @@
         <v>73</v>
       </c>
       <c r="U164" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="V164" t="s" s="2">
         <v>73</v>
@@ -22217,11 +22223,11 @@
         <v>73</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z164" s="2"/>
       <c r="AA164" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AB164" t="s" s="2">
         <v>73</v>
@@ -22239,7 +22245,7 @@
         <v>73</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>79</v>
@@ -22256,13 +22262,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -22285,13 +22291,13 @@
         <v>73</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
@@ -22342,7 +22348,7 @@
         <v>73</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>79</v>
@@ -22359,13 +22365,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -22391,10 +22397,10 @@
         <v>89</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -22445,7 +22451,7 @@
         <v>73</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>74</v>
@@ -22462,13 +22468,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -22494,10 +22500,10 @@
         <v>89</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
@@ -22548,7 +22554,7 @@
         <v>73</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>74</v>
@@ -22565,13 +22571,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -22594,13 +22600,13 @@
         <v>73</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -22651,7 +22657,7 @@
         <v>73</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>79</v>
@@ -22668,13 +22674,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22697,13 +22703,13 @@
         <v>73</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
@@ -22754,7 +22760,7 @@
         <v>73</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>79</v>
@@ -22771,13 +22777,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22800,13 +22806,13 @@
         <v>73</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -22857,7 +22863,7 @@
         <v>73</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>79</v>
@@ -22874,13 +22880,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -22903,13 +22909,13 @@
         <v>73</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
@@ -22936,11 +22942,11 @@
         <v>73</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z171" s="2"/>
       <c r="AA171" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AB171" t="s" s="2">
         <v>73</v>
@@ -22958,7 +22964,7 @@
         <v>73</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>79</v>
@@ -22975,13 +22981,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -23004,13 +23010,13 @@
         <v>73</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -23061,7 +23067,7 @@
         <v>73</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>79</v>
@@ -23078,13 +23084,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -23107,13 +23113,13 @@
         <v>73</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
@@ -23164,7 +23170,7 @@
         <v>73</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>74</v>
@@ -23181,13 +23187,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -23213,10 +23219,10 @@
         <v>89</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -23267,7 +23273,7 @@
         <v>73</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>74</v>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/all-profiles.xlsx
+++ b/add-info-dmp/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
